--- a/src/main/resources/account/default/BAS-2026---Enskild-firma-ej-K1.xlsx
+++ b/src/main/resources/account/default/BAS-2026---Enskild-firma-ej-K1.xlsx
@@ -427,6 +427,9 @@
           <t>BAS 2026 - Enskild firma, ej K1</t>
         </is>
       </c>
+      <c r="C1" t="inlineStr"/>
+      <c r="D1" t="inlineStr"/>
+      <c r="E1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -439,6 +442,9 @@
           <t>EUBAS97</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -451,6 +457,9 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -461,6 +470,9 @@
       <c r="B4" t="n">
         <v>6</v>
       </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2776,7 +2788,11 @@
           <t>Pågående arbeten, nedlagda kostnader</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr"/>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="D140" t="inlineStr">
         <is>
           <t>7240</t>
@@ -6345,7 +6361,11 @@
           <t>Kortfristiga lån från kreditinstitut</t>
         </is>
       </c>
-      <c r="C361" t="inlineStr"/>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>U1</t>
+        </is>
+      </c>
       <c r="D361" t="inlineStr">
         <is>
           <t>7380</t>
@@ -6362,7 +6382,11 @@
           <t>Byggnadskreditiv, kortfristig del</t>
         </is>
       </c>
-      <c r="C362" t="inlineStr"/>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>U1</t>
+        </is>
+      </c>
       <c r="D362" t="inlineStr">
         <is>
           <t>7380</t>
@@ -6430,7 +6454,11 @@
           <t>Ej inlösta presentkort</t>
         </is>
       </c>
-      <c r="C366" t="inlineStr"/>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>U2</t>
+        </is>
+      </c>
       <c r="D366" t="inlineStr">
         <is>
           <t>7383</t>
@@ -6481,7 +6509,11 @@
           <t>Pågående arbeten, fakturering</t>
         </is>
       </c>
-      <c r="C369" t="inlineStr"/>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>U3</t>
+        </is>
+      </c>
       <c r="D369" t="inlineStr">
         <is>
           <t>7383</t>
@@ -6946,7 +6978,11 @@
           <t>Utgående moms, 25 %</t>
         </is>
       </c>
-      <c r="C398" t="inlineStr"/>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>U1</t>
+        </is>
+      </c>
       <c r="D398" t="inlineStr">
         <is>
           <t>7383</t>
@@ -6963,7 +6999,11 @@
           <t>Utgående moms på försäljning inom Sverige, 25 %</t>
         </is>
       </c>
-      <c r="C399" t="inlineStr"/>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>U1</t>
+        </is>
+      </c>
       <c r="D399" t="inlineStr">
         <is>
           <t>7383</t>
@@ -6980,7 +7020,11 @@
           <t>Utgående moms på egna uttag, 25 %</t>
         </is>
       </c>
-      <c r="C400" t="inlineStr"/>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>U1</t>
+        </is>
+      </c>
       <c r="D400" t="inlineStr">
         <is>
           <t>7383</t>
@@ -6997,7 +7041,11 @@
           <t>Utgående moms för uthyrning, 25 %</t>
         </is>
       </c>
-      <c r="C401" t="inlineStr"/>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>U1</t>
+        </is>
+      </c>
       <c r="D401" t="inlineStr">
         <is>
           <t>7383</t>
@@ -7014,7 +7062,11 @@
           <t>Utgående moms omvänd betalskyldighet, 25 %</t>
         </is>
       </c>
-      <c r="C402" t="inlineStr"/>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>U1MI</t>
+        </is>
+      </c>
       <c r="D402" t="inlineStr">
         <is>
           <t>7383</t>
@@ -7031,7 +7083,11 @@
           <t>Utgående moms import av varor, 25 %</t>
         </is>
       </c>
-      <c r="C403" t="inlineStr"/>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>U1MI</t>
+        </is>
+      </c>
       <c r="D403" t="inlineStr">
         <is>
           <t>7383</t>
@@ -7065,7 +7121,11 @@
           <t>Vilande utgående moms, 25 %</t>
         </is>
       </c>
-      <c r="C405" t="inlineStr"/>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>U1</t>
+        </is>
+      </c>
       <c r="D405" t="inlineStr">
         <is>
           <t>7383</t>
@@ -7099,7 +7159,11 @@
           <t>Utgående moms på försäljning inom Sverige, 12 %</t>
         </is>
       </c>
-      <c r="C407" t="inlineStr"/>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>U2</t>
+        </is>
+      </c>
       <c r="D407" t="inlineStr">
         <is>
           <t>7383</t>
@@ -7116,7 +7180,11 @@
           <t>Utgående moms på egna uttag, 12 %</t>
         </is>
       </c>
-      <c r="C408" t="inlineStr"/>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>U2</t>
+        </is>
+      </c>
       <c r="D408" t="inlineStr">
         <is>
           <t>7383</t>
@@ -7150,7 +7218,11 @@
           <t>Utgående moms omvänd betalningsskyldighet 12 %</t>
         </is>
       </c>
-      <c r="C410" t="inlineStr"/>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>U2MI</t>
+        </is>
+      </c>
       <c r="D410" t="inlineStr">
         <is>
           <t>7383</t>
@@ -7167,7 +7239,11 @@
           <t>Utgående moms import av varor, 12 %</t>
         </is>
       </c>
-      <c r="C411" t="inlineStr"/>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>U2MI</t>
+        </is>
+      </c>
       <c r="D411" t="inlineStr">
         <is>
           <t>7383</t>
@@ -7201,7 +7277,11 @@
           <t>Vilande utgående moms, 12 %</t>
         </is>
       </c>
-      <c r="C413" t="inlineStr"/>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>U2</t>
+        </is>
+      </c>
       <c r="D413" t="inlineStr">
         <is>
           <t>7383</t>
@@ -7235,7 +7315,11 @@
           <t>Utgående moms på försäljning inom Sverige, 6 %</t>
         </is>
       </c>
-      <c r="C415" t="inlineStr"/>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>U3</t>
+        </is>
+      </c>
       <c r="D415" t="inlineStr">
         <is>
           <t>7383</t>
@@ -7252,7 +7336,11 @@
           <t>Utgående moms på egna uttag, 6 %</t>
         </is>
       </c>
-      <c r="C416" t="inlineStr"/>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>U3</t>
+        </is>
+      </c>
       <c r="D416" t="inlineStr">
         <is>
           <t>7383</t>
@@ -7286,7 +7374,11 @@
           <t>Utgående moms omvänd betalningsskyldighet, 6 %</t>
         </is>
       </c>
-      <c r="C418" t="inlineStr"/>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>U3MI</t>
+        </is>
+      </c>
       <c r="D418" t="inlineStr">
         <is>
           <t>7383</t>
@@ -7303,7 +7395,11 @@
           <t>Utgående moms import av varor, 6 %</t>
         </is>
       </c>
-      <c r="C419" t="inlineStr"/>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>U3MI</t>
+        </is>
+      </c>
       <c r="D419" t="inlineStr">
         <is>
           <t>7383</t>
@@ -7337,7 +7433,11 @@
           <t>Vilande utgående moms, 6 %</t>
         </is>
       </c>
-      <c r="C421" t="inlineStr"/>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>U3</t>
+        </is>
+      </c>
       <c r="D421" t="inlineStr">
         <is>
           <t>7383</t>
@@ -7354,7 +7454,11 @@
           <t>Ingående moms</t>
         </is>
       </c>
-      <c r="C422" t="inlineStr"/>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="D422" t="inlineStr">
         <is>
           <t>7383</t>
@@ -7371,7 +7475,11 @@
           <t>Debiterad ingående moms</t>
         </is>
       </c>
-      <c r="C423" t="inlineStr"/>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="D423" t="inlineStr">
         <is>
           <t>7383</t>
@@ -7388,7 +7496,11 @@
           <t>Debiterad ingående moms i anslutning till frivillig betalningsskyldighet</t>
         </is>
       </c>
-      <c r="C424" t="inlineStr"/>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="D424" t="inlineStr">
         <is>
           <t>7383</t>
@@ -7405,7 +7517,11 @@
           <t>Beräknad ingående moms på förvärv från utlandet</t>
         </is>
       </c>
-      <c r="C425" t="inlineStr"/>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="D425" t="inlineStr">
         <is>
           <t>7383</t>
@@ -7422,7 +7538,11 @@
           <t>Ingående moms på uthyrning</t>
         </is>
       </c>
-      <c r="C426" t="inlineStr"/>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="D426" t="inlineStr">
         <is>
           <t>7383</t>
@@ -7456,7 +7576,11 @@
           <t>Vilande ingående moms</t>
         </is>
       </c>
-      <c r="C428" t="inlineStr"/>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="D428" t="inlineStr">
         <is>
           <t>7383</t>
@@ -7473,7 +7597,11 @@
           <t>Ingående moms, blandad verksamhet</t>
         </is>
       </c>
-      <c r="C429" t="inlineStr"/>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="D429" t="inlineStr">
         <is>
           <t>7383</t>
@@ -9109,7 +9237,11 @@
           <t>Fakturerade kostnader (gruppkonto)</t>
         </is>
       </c>
-      <c r="C529" t="inlineStr"/>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>MP1</t>
+        </is>
+      </c>
       <c r="D529" t="inlineStr"/>
       <c r="E529" t="inlineStr"/>
     </row>
@@ -9122,7 +9254,11 @@
           <t>Fakturerat emballage</t>
         </is>
       </c>
-      <c r="C530" t="inlineStr"/>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>MP1</t>
+        </is>
+      </c>
       <c r="D530" t="inlineStr"/>
       <c r="E530" t="inlineStr"/>
     </row>
@@ -9161,7 +9297,11 @@
           <t>Fakturerade frakter</t>
         </is>
       </c>
-      <c r="C533" t="inlineStr"/>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>MP1</t>
+        </is>
+      </c>
       <c r="D533" t="inlineStr"/>
       <c r="E533" t="inlineStr"/>
     </row>
@@ -9187,7 +9327,11 @@
           <t>Fakturerade frakter, export</t>
         </is>
       </c>
-      <c r="C535" t="inlineStr"/>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>VTEU</t>
+        </is>
+      </c>
       <c r="D535" t="inlineStr"/>
       <c r="E535" t="inlineStr"/>
     </row>
@@ -9200,7 +9344,11 @@
           <t>Fakturerade tull- och  speditionskostnader m.m.</t>
         </is>
       </c>
-      <c r="C536" t="inlineStr"/>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
       <c r="D536" t="inlineStr"/>
       <c r="E536" t="inlineStr"/>
     </row>
@@ -9213,7 +9361,11 @@
           <t>Faktureringsavgifter</t>
         </is>
       </c>
-      <c r="C537" t="inlineStr"/>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>MP1</t>
+        </is>
+      </c>
       <c r="D537" t="inlineStr"/>
       <c r="E537" t="inlineStr"/>
     </row>
@@ -9226,7 +9378,11 @@
           <t>Faktureringsavgifter, EU-land</t>
         </is>
       </c>
-      <c r="C538" t="inlineStr"/>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
       <c r="D538" t="inlineStr"/>
       <c r="E538" t="inlineStr"/>
     </row>
@@ -9239,7 +9395,11 @@
           <t>Faktureringsavgifter, export</t>
         </is>
       </c>
-      <c r="C539" t="inlineStr"/>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>VTEU</t>
+        </is>
+      </c>
       <c r="D539" t="inlineStr"/>
       <c r="E539" t="inlineStr"/>
     </row>
@@ -9252,7 +9412,11 @@
           <t>Fakturerade resekostnader</t>
         </is>
       </c>
-      <c r="C540" t="inlineStr"/>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>MP1</t>
+        </is>
+      </c>
       <c r="D540" t="inlineStr"/>
       <c r="E540" t="inlineStr"/>
     </row>
@@ -9265,7 +9429,11 @@
           <t>Fakturerade kostnader till  koncernföretag</t>
         </is>
       </c>
-      <c r="C541" t="inlineStr"/>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>MP1</t>
+        </is>
+      </c>
       <c r="D541" t="inlineStr"/>
       <c r="E541" t="inlineStr"/>
     </row>
@@ -9317,7 +9485,11 @@
           <t>Fakturerade kostnader till  intresseföretag, gemensamt styrda företag och övriga företag som det finns ett ägarintresse i</t>
         </is>
       </c>
-      <c r="C545" t="inlineStr"/>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>MP1</t>
+        </is>
+      </c>
       <c r="D545" t="inlineStr"/>
       <c r="E545" t="inlineStr"/>
     </row>
@@ -9330,7 +9502,11 @@
           <t>Övriga fakturerade kostnader</t>
         </is>
       </c>
-      <c r="C546" t="inlineStr"/>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>MP1</t>
+        </is>
+      </c>
       <c r="D546" t="inlineStr"/>
       <c r="E546" t="inlineStr"/>
     </row>
@@ -9343,7 +9519,11 @@
           <t>Rörelsens sidointäkter (gruppkonto)</t>
         </is>
       </c>
-      <c r="C547" t="inlineStr"/>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>MP1</t>
+        </is>
+      </c>
       <c r="D547" t="inlineStr"/>
       <c r="E547" t="inlineStr"/>
     </row>
@@ -9356,7 +9536,11 @@
           <t>Försäljning av material</t>
         </is>
       </c>
-      <c r="C548" t="inlineStr"/>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>MP1</t>
+        </is>
+      </c>
       <c r="D548" t="inlineStr"/>
       <c r="E548" t="inlineStr"/>
     </row>
@@ -9421,7 +9605,11 @@
           <t>Tillfällig uthyrning av personal</t>
         </is>
       </c>
-      <c r="C553" t="inlineStr"/>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>MP1</t>
+        </is>
+      </c>
       <c r="D553" t="inlineStr"/>
       <c r="E553" t="inlineStr"/>
     </row>
@@ -9512,7 +9700,11 @@
           <t>Övriga sidointäkter</t>
         </is>
       </c>
-      <c r="C560" t="inlineStr"/>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>MP1</t>
+        </is>
+      </c>
       <c r="D560" t="inlineStr"/>
       <c r="E560" t="inlineStr"/>
     </row>
@@ -9525,7 +9717,11 @@
           <t>Intäktskorrigeringar (gruppkonto)</t>
         </is>
       </c>
-      <c r="C561" t="inlineStr"/>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>MP1</t>
+        </is>
+      </c>
       <c r="D561" t="inlineStr"/>
       <c r="E561" t="inlineStr"/>
     </row>
@@ -9538,7 +9734,11 @@
           <t>Ofördelade intäktsreduktioner</t>
         </is>
       </c>
-      <c r="C562" t="inlineStr"/>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>MP1</t>
+        </is>
+      </c>
       <c r="D562" t="inlineStr"/>
       <c r="E562" t="inlineStr"/>
     </row>
@@ -9551,7 +9751,11 @@
           <t>Lämnade rabatter</t>
         </is>
       </c>
-      <c r="C563" t="inlineStr"/>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>MP1</t>
+        </is>
+      </c>
       <c r="D563" t="inlineStr"/>
       <c r="E563" t="inlineStr"/>
     </row>
@@ -9607,7 +9811,11 @@
           <t>Punktskatter</t>
         </is>
       </c>
-      <c r="C567" t="inlineStr"/>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>MP1</t>
+        </is>
+      </c>
       <c r="D567" t="inlineStr"/>
       <c r="E567" t="inlineStr"/>
     </row>
@@ -9646,7 +9854,11 @@
           <t>Övriga intäktskorrigeringar</t>
         </is>
       </c>
-      <c r="C570" t="inlineStr"/>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>MP1</t>
+        </is>
+      </c>
       <c r="D570" t="inlineStr"/>
       <c r="E570" t="inlineStr"/>
     </row>
@@ -9693,7 +9905,11 @@
           <t>Aktiverat arbete (omkostnader)</t>
         </is>
       </c>
-      <c r="C573" t="inlineStr"/>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>MF</t>
+        </is>
+      </c>
       <c r="D573" t="inlineStr">
         <is>
           <t>7403</t>
@@ -9727,7 +9943,11 @@
           <t>Övriga rörelseintäkter (gruppkonto)</t>
         </is>
       </c>
-      <c r="C575" t="inlineStr"/>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>MP1</t>
+        </is>
+      </c>
       <c r="D575" t="inlineStr"/>
       <c r="E575" t="inlineStr"/>
     </row>
@@ -9870,7 +10090,11 @@
           <t>Återvunna, tidigare avskrivna  kundfordringar</t>
         </is>
       </c>
-      <c r="C586" t="inlineStr"/>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>MF</t>
+        </is>
+      </c>
       <c r="D586" t="inlineStr"/>
       <c r="E586" t="inlineStr"/>
     </row>
@@ -9948,7 +10172,11 @@
           <t>Erhållna offentliga bidrag</t>
         </is>
       </c>
-      <c r="C592" t="inlineStr"/>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>MF</t>
+        </is>
+      </c>
       <c r="D592" t="inlineStr"/>
       <c r="E592" t="inlineStr"/>
     </row>
@@ -10026,7 +10254,11 @@
           <t>Övriga ersättningar, bidrag och  intäkter</t>
         </is>
       </c>
-      <c r="C598" t="inlineStr"/>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>MF</t>
+        </is>
+      </c>
       <c r="D598" t="inlineStr"/>
       <c r="E598" t="inlineStr"/>
     </row>
